--- a/光伏配储项目/电价数据/2026/升平站.xlsx
+++ b/光伏配储项目/电价数据/2026/升平站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.4903</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38453</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.75518</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.54963</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5615399999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.49089</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.48383</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.4271</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.44217</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.41894</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.41166</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41032</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.41177</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.40317</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.3842</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.37836</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.40872</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.41216</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.40585</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.41543</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.40482</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.43226</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.47658</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.21379</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.23775</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.10378</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.23907</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.00109</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.09965</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.07174</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.18058</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.18454</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.16994</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.15131</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.05778</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.40078</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5246499999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.53307</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.73361</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.1159</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39476</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.15281</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43152</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43765</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.66087</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.85824</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.46685</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.18988</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.49275</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.34476</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.9966699999999999</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.27469</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.56394</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.43004</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.67602</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.72634</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.10518</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.96685</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8896000000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79988</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7606799999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51509</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48291</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46542</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41738</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42724</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.71596</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.88681</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9385399999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.50144</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5234800000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50851</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50866</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49069</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40208</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47226</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38276</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.42092</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37793</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36353</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.37718</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.39187</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.44085</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.11231</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.96839</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.0362</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.48657</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.48076</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41688</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50499</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.31151</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.19653</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.20406</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.28414</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.11856</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.20772</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.5176000000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.7032999999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.00217</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.04284</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.7237</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.63924</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.01068</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.02619</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.39941</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.8458</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.23586</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.44926</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.65943</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.59782</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7460800000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.75707</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.15969</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.24137</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.13829</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.83876</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20379</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.10492</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.25611</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.02396</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.08926</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.64959</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.98214</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.91227</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.9582200000000001</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.78652</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.90062</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.74585</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.77378</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45106</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7376200000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.76873</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45083</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4296</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44503</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37691</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33489</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5124</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.49227</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48947</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36877</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44525</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41536</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39131</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43105</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44704</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36871</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37618</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36413</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39905</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47698</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44608</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44112</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39625</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.39847</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.39318</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.22888</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.0036</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.28186</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.07471999999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.5006</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.13791</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.46353</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.52583</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.45909</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.78359</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.44981</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.53039</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.4475</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42929</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.43686</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.45389</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.45345</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5338999999999999</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.5242100000000001</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.44903</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.47195</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.28233</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.62042</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.64019</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46555</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50602</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.48041</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.56165</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.50426</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.61818</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.40246</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42368</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48331</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61654</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.58502</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.55843</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.7254400000000001</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.6093099999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5258700000000001</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.42846</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.56396</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43539</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45829</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39805</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34228</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5161399999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.50151</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44005</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39293</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39208</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39198</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38965</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45179</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38873</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39034</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37827</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43038</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.40367</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.15784</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.11853</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.22786</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.1155</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.56814</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.39497</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.17588</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.17577</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.1696</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.62095</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.45091</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.2825299999999999</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.42125</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.47679</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.44642</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.50737</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46628</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40173</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47499</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.49237</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.55348</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.43888</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.55657</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.49032</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46655</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50402</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42525</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40487</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42132</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32087</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.38127</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38161</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31109</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28946</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.16806</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.2756</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.09823</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.27287</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.17062</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.1178</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13519</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.16201</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.04243</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.21114</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.21026</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.08426</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.03406</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04717</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.0148</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.24576</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.41377</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.41523</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.41261</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.39089</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.42559</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.41919</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.4319</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.48255</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38422</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.41901</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.53714</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.36738</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.3702</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.81636</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.44864</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.54598</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.50892</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.51949</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.39348</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.37195</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.40138</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.40934</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.40758</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.55744</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.36176</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.38668</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.38867</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.41114</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10223</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04324</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04487</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.006990000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20044</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04639</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.26691</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.16139</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.033</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05459000000000001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05277</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.34498</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32219</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28565</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37453</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42885</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45751</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31266</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78544</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88747</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86902</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.56368</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33082</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03289</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53076</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5388200000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77295</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49313</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39986</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20696</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62182</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45032</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41994</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40342</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.3884</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.42793</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.45095</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.44535</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45416</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.41779</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.43806</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.6512</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.48913</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.6214</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.7989400000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8832000000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47064</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.48065</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.64932</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.48901</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.0122</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.76675</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.87137</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87502</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.50014</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.86127</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.8058999999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59121</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.36889</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.46252</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.46631</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.5222899999999999</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.46968</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.43357</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.41637</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.36803</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9325599999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.38616</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.5156900000000001</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.46523</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.44717</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.53431</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.41473</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.45713</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.45316</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.59028</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.38296</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.43196</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.36602</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.38354</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.40643</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.38642</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.23658</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28676</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.10679</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30411</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.31259</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.27957</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26903</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20041</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29895</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28531</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3146600000000001</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.36884</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.42617</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37181</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25798</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.3762200000000001</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27901</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.42211</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.5152899999999999</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.36501</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42685</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.46917</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.46517</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.45019</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.45128</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.74479</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.41555</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.93577</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.47799</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.19381</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.72385</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.81555</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.67503</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.7574299999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.56676</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.47098</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.52188</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.45983</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.48539</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.43503</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.43109</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.46727</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.59099</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.43079</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.45287</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.46975</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.45249</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.40587</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.49631</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.52928</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.41386</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4406</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.5038899999999999</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.43075</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.42788</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.45446</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.4933999999999999</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.41627</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.45981</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5127699999999999</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.37765</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.43591</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.41657</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.6141599999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.5077699999999999</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25128</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15704</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.2879</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27572</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01584</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26382</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25824</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2842</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29451</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.44046</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.43791</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38647</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.40334</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.37921</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.63578</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.53089</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.9853099999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.53649</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.50459</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.40984</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.50051</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.42152</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.39804</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.36039</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.49887</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.38162</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.42791</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.39434</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.39703</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.39776</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.39171</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.40814</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.36351</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.40511</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.40488</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.49581</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.38988</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.48994</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.50532</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.42407</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.50251</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.47077</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.41336</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.42253</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.38469</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.38989</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.21696</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.08688</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.10831</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28229</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.12311</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.09623000000000001</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.10188</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26351</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.11119</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.23388</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.09873</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25565</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.29226</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14229</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.06784999999999999</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.04606</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.07662000000000001</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.07162</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.16944</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.08943000000000001</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28631</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.38836</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.38455</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.41431</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.41662</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.44365</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.39335</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.42838</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.52485</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.45068</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.43532</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.45342</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.44482</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.52542</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.51188</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.50854</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.5147699999999999</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.45856</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.41833</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.4062</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.41278</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.4065299999999999</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.39617</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.39584</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.38206</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.65118</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.40337</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.54715</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.48063</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.46975</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.40574</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.42083</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.41799</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.43576</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.41602</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.43297</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.40333</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.42145</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.38291</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.36301</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.36301</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.37497</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.5245</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.40754</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.42014</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.36934</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.26902</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26792</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.24429</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.18319</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.23046</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.22077</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.17015</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.21302</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.26077</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29416</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27445</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.25392</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.6315</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.39851</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.49879</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.41271</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.38332</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.40064</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.37559</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.38388</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.46197</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.39173</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.39467</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.42633</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.41601</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.3876</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.6066900000000001</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.41466</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.41105</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.39326</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.36623</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.36509</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.4249</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.39469</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.41197</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.40531</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.38241</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.44526</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.14278</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.42383</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.67648</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.50586</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.44635</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.38129</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.45919</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.41916</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25626</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.1932</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.02701</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.29159</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.22499</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.5779099999999999</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25863</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.27545</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.40575</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.02048</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.39345</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.4296</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.5829500000000001</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.47532</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46001</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.44158</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7138600000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.9931599999999999</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.8537899999999999</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.69394</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.38955</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.52462</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.2652</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.40304</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.60476</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.40751</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.39286</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.4987</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.42545</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.41429</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.41647</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.39738</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.41195</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.40488</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.42444</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.44223</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.42311</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.41876</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39513</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.39539</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.42216</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.39219</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.38157</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.36824</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.37519</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45245</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.41853</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.38301</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.41166</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.37611</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.41404</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.44486</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.43393</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.38682</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.48484</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.43079</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.38335</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.43789</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.44342</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.40669</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3646</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.36307</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.36533</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36433</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.36498</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.38373</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.36433</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.54752</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.38139</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.36866</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.41224</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.38233</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.37286</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.37951</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.36423</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.36482</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.37371</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.3766600000000001</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.40954</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.41934</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.41313</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.41455</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.47795</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.43014</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.40887</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39074</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6710700000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.01617</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.50888</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.5283300000000001</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.44643</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.37384</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.36779</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.42669</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.39183</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.39589</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.3776</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.37474</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.37365</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.38375</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.37453</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.38529</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.38424</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.37503</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.41587</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.37433</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.37206</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.41558</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.39543</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.37203</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.37346</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.36871</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26098</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.11452</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.20709</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.18279</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.14091</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.19255</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.22485</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.22654</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.25785</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.16695</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.22491</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.26394</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.25455</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.27862</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.40438</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.28609</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29641</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.37289</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38789</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.41325</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.44648</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.5370499999999999</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.47765</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.4581</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.67362</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.63124</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.64635</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.61703</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8414700000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.59409</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.12122</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.6244299999999999</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.5175</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.42916</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.41071</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.43921</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.5797899999999999</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.48957</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.47247</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.38396</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.57092</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.6976</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.60866</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.8626900000000001</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.4660899999999999</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.44505</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.45803</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.45233</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.46589</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.43851</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.40979</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.44957</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.44709</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.42823</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.40315</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.47449</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.42817</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.47173</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.43182</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.45776</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.44953</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.46487</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.45353</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.5370499999999999</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.5272100000000001</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.69675</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.59923</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.52224</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.5895499999999999</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.5186799999999999</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.4645</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.38477</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.40726</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.43191</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.46856</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.46776</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.54914</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.44966</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.41096</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.45741</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.4391600000000001</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.4282</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.37349</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.39706</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.64739</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.77889</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.36934</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.38732</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.40272</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.3747799999999999</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.40736</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.41042</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.42136</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.42734</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.46008</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.49399</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.57711</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.5195299999999999</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.61229</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.6143099999999999</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.67526</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.9003099999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.10906</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.22175</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.8807</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.04367</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.87233</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.66411</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.08323</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7847799999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.63824</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.68745</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.5397000000000001</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.56826</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.5670700000000001</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.55652</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.5484600000000001</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.46588</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.6667999999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.48249</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.5035299999999999</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.5261699999999999</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.44951</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.43945</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.51209</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.43118</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.4431</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.55167</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.45412</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.46272</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.4259</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.41062</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.40788</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.37206</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.38103</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.5699500000000001</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.41992</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.38103</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.44272</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.44496</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.39458</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.37645</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.39457</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40715</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.40033</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.41459</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.43248</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.40178</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.39278</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.39464</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.25615</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.41595</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.5771799999999999</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.09307</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.25287</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36464</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.43469</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.4029</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.50688</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.44874</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.00843</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.12291</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.05801</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29189</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.37194</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.37199</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.40638</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.42339</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.43504</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.39675</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.47625</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.44989</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.45005</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43255</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.5081600000000001</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.42312</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.45608</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.47143</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.48124</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4975</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.47999</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.3905</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.44652</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.39195</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.45964</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.42292</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.45719</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.48397</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.41614</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.45907</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.5011</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.48262</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.44591</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.59976</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.47498</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.47733</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.44151</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.46107</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.44423</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.5742200000000001</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.40564</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.54573</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.5403300000000001</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.4439</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.5520700000000001</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.42093</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.44326</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.51734</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.42068</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.43145</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.41403</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.42563</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.4318</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.43798</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.5033</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.44416</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.50163</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.51454</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.4689</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.38744</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.4023</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.51371</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.36539</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.37366</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29673</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.19094</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.21723</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.21846</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.25637</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.40888</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.23374</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.06520000000000001</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29659</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.27204</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.10564</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.12489</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.29764</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.19298</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.23017</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.27119</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21822</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27654</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28563</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.38324</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.41453</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.38041</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.42037</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.37597</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.43454</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.44801</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.39332</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.43844</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.40047</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.43673</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.40428</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.45416</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.47718</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.45106</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.40949</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.42877</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.38645</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.42006</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.46273</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.47727</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.39314</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.43829</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.43885</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.40901</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.47622</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.39077</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.46487</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.44378</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.47394</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.46706</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.46706</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.46131</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.46131</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.46475</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.46695</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.46131</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.46187</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.37552</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.47422</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.47381</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.4779</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.03021</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00073</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15072</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02253</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01495</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04305</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04098</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04863</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04829</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02943</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.0398</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00132</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27839</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03656</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01554</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03567</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20502</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26829</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28029</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.4714100000000001</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.3826</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.36437</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.38189</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.41225</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.51954</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.41866</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38168</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.39641</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.10951</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.95166</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.47515</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.7995800000000001</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.50344</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.51924</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.56557</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.43581</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.47949</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.36443</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.44342</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.45607</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.45064</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.57778</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.43819</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.41303</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.59846</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.51428</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.58714</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.54001</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.59189</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.5594600000000001</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.5493300000000001</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.57199</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.61063</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.46063</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.50795</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40212</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.53801</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.49541</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.36397</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.31047</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.90511</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86897</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.41029</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.13157</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.24848</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.0679</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.0094</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.03431</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.02252</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.25469</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.04878</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04307</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.01346</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.03818</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30248</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.00843</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.03702</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.01196</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.03639</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25445</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.40206</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.41889</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.43796</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.40431</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.39114</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.43951</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.00014</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.08428</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.05223</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.77576</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.99681</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.07308</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.00958</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.0852</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8588899999999999</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.85714</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8613</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.95817</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.07385</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.08117</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.06968</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.39284</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.41205</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.41189</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.5804400000000001</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.8432200000000001</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.32508</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.79174</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.5144299999999999</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.5951900000000001</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.49887</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.49733</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.46673</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.50025</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.39729</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.39526</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.40981</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.6329600000000001</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.42485</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.44488</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.41567</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.43261</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.4377200000000001</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.5608500000000001</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.50281</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.4781</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.48107</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.5889099999999999</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.6373799999999999</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.47386</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.49924</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.38041</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.47545</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.39885</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.5009400000000001</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.42586</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.42859</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.10278</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.1083</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.10034</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.42097</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.26003</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26109</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31334</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.37368</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.41454</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.42288</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.41239</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.40752</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.4086</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.44682</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.60017</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>1.15825</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.49016</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.86075</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.58733</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.43674</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.5267200000000001</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.51774</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.47286</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.6429</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.39281</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.48536</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.50003</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.4724100000000001</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.46453</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.44367</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.43801</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.43245</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.39742</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.40836</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.39903</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39091</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.38361</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.36484</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.37565</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.37117</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.37229</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.37237</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.38722</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.37583</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.39814</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.38842</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.39887</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.39721</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5255</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.42572</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.4086</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.80855</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.9722000000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.7892899999999999</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.20365</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.73368</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.56664</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.40052</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36279</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.37566</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.4108</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36714</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.30693</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39229</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.41053</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.89091</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8272</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.46007</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.4569</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.5571699999999999</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5529500000000001</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.6249400000000001</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.81729</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.55084</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.88981</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.7673300000000001</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.5867100000000001</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.58873</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.43438</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.44906</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.5143799999999999</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.40472</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.38803</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.52054</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.43783</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.39207</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.4377</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.40624</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.27492</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.38708</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.39493</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.51798</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.43315</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.43981</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.42769</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.41755</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.38322</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.40689</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.40833</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.40664</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.3988</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.38347</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.37461</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.40383</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.44643</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.41141</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.37955</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.37414</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.37279</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.38435</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.40354</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39072</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43426</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.3781600000000001</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36359</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.28678</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.39493</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.38034</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.40399</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.39128</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39416</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.40308</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.42692</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.39607</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.40673</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.44094</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.44778</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.48194</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.6593600000000001</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.6456000000000001</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.7493</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.53365</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.39626</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.75048</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.4662</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.91391</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.48681</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.48016</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.4928</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.97661</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.46338</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.48435</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.42906</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.39725</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.39901</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38361</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.39461</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.37366</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3637</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.39199</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.38431</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.37369</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.4439</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.35601</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.55367</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.37192</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.38314</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.41222</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.4073</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.39937</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.38649</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.38325</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.43267</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.38571</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.36433</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.17704</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.27181</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.29015</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.17431</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.20735</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.09204000000000001</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.1948</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.00396</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.0554</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26494</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.02582</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06826</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.05014</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.11056</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.04888</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.23185</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.18296</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.20766</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.37734</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.38739</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.38416</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.42498</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.39342</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.39003</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.39502</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.41472</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.53123</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.43465</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.44757</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.50778</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.46822</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.43135</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.41965</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42369</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.40821</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.41773</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.4391600000000001</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.46876</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.40236</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.39472</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.39467</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38639</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.41052</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.20811</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.42719</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.16484</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.43824</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.42244</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.26812</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.4091</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.41225</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.40896</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.40405</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.40075</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.39908</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.39559</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.40975</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.40056</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.40073</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.39842</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.39496</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.39201</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.39447</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.39359</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.39091</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.38453</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.38383</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.40501</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.39071</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.2303</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.2627</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33416</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.27355</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.30157</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.07177</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.11243</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.28287</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.30279</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.41077</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.40669</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.41743</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.42657</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38845</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40282</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.40451</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.37837</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.37201</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.42475</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.42874</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.40233</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.41072</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39371</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.41564</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.40727</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.42051</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39122</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.41097</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.4049700000000001</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.41332</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38336</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.38221</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.38241</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38446</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.47213</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.40811</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.44123</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37275</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.39956</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.39912</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.40413</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.40082</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39122</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.38838</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38681</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.39402</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.39234</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.38641</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.38522</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.37512</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.37739</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17662</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14626</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19939</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.00457</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.24875</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.02557</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.008619999999999999</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.03378</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.009710000000000002</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.13709</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.03337</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.09247</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18076</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.02619</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22858</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26809</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15796</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.27015</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.00318</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.23695</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.06842000000000001</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20071</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14712</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26556</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.25735</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.36316</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.40815</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.37641</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.38797</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.41971</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.4112</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.41895</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37582</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.40293</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.42366</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.41399</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40158</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.42574</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.5032099999999999</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39686</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.41401</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41215</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38166</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40592</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.40479</v>
       </c>
     </row>
   </sheetData>
